--- a/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
+++ b/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b234acbc490037a6/Desktop/Projetos/Uni.co/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB624F6E-CF3D-491E-9697-643523E31C66}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F59B22-2DA0-40D5-A35D-413E3E39D3EA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
   </bookViews>
   <sheets>
     <sheet name="Apuração" sheetId="9" r:id="rId1"/>
@@ -9305,6 +9305,217 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0042E7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="hair">
+          <color auto="1"/>
+        </left>
+        <right style="hair">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -9559,217 +9770,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0042E7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10529,24 +10529,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="89">
   <autoFilter ref="B30:I34" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5330A6FC-1100-458A-AA09-9E9F571349FC}" name="TODOS"/>
-    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="76" dataCellStyle="Porcentagem"/>
-    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="75" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="74" dataCellStyle="Porcentagem"/>
-    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="73" dataCellStyle="Porcentagem"/>
-    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="72" dataCellStyle="Porcentagem"/>
-    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="71" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="70" dataCellStyle="Porcentagem"/>
+    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="88" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="87" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="86" dataCellStyle="Porcentagem"/>
+    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="85" dataCellStyle="Porcentagem"/>
+    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="84" dataCellStyle="Porcentagem"/>
+    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="83" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="82" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="81">
   <autoFilter ref="B48:D52" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{967F361C-5A9B-44CE-BA60-DBCCC368C089}" name="Estado"/>
@@ -10558,41 +10558,47 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
-  <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79">
+  <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="BW"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="66"/>
-    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="63"/>
-    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="61" dataCellStyle="Vírgula"/>
-    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="60" dataCellStyle="Vírgula"/>
-    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="59" dataCellStyle="Vírgula"/>
-    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="58" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="57" dataCellStyle="Vírgula"/>
-    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="56" dataCellStyle="Porcentagem"/>
-    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="54" dataCellStyle="Porcentagem"/>
+    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="78"/>
+    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="75"/>
+    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="73" dataCellStyle="Vírgula"/>
+    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="72" dataCellStyle="Vírgula"/>
+    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="71" dataCellStyle="Vírgula"/>
+    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="70" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="69" dataCellStyle="Vírgula"/>
+    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="68" dataCellStyle="Porcentagem"/>
+    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="66" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="B8:K320" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="85"/>
-    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="83"/>
-    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="82"/>
-    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="81"/>
-    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="79"/>
-    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="78" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="54" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11833,7 +11839,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" s="89" t="s">
         <v>80</v>
       </c>
@@ -11874,7 +11880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" s="89" t="s">
         <v>80</v>
       </c>
@@ -11915,7 +11921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B12" s="89" t="s">
         <v>80</v>
       </c>
@@ -11956,7 +11962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B13" s="89" t="s">
         <v>80</v>
       </c>
@@ -11997,7 +12003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" s="89" t="s">
         <v>80</v>
       </c>
@@ -12038,7 +12044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" s="89" t="s">
         <v>80</v>
       </c>
@@ -12079,7 +12085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" s="89" t="s">
         <v>80</v>
       </c>
@@ -12120,7 +12126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" s="89" t="s">
         <v>80</v>
       </c>
@@ -12161,7 +12167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" s="89" t="s">
         <v>80</v>
       </c>
@@ -12202,7 +12208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" s="89" t="s">
         <v>80</v>
       </c>
@@ -12243,7 +12249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" s="89" t="s">
         <v>80</v>
       </c>
@@ -12284,7 +12290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" s="89" t="s">
         <v>80</v>
       </c>
@@ -12325,7 +12331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" s="89" t="s">
         <v>80</v>
       </c>
@@ -12366,7 +12372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" s="89" t="s">
         <v>80</v>
       </c>
@@ -12407,7 +12413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" s="89" t="s">
         <v>80</v>
       </c>
@@ -12448,7 +12454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" s="89" t="s">
         <v>80</v>
       </c>
@@ -12489,7 +12495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" s="89" t="s">
         <v>80</v>
       </c>
@@ -12530,7 +12536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" s="89" t="s">
         <v>80</v>
       </c>

--- a/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
+++ b/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F59B22-2DA0-40D5-A35D-413E3E39D3EA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
+    <workbookView xWindow="4800" yWindow="585" windowWidth="14355" windowHeight="9075" activeTab="1" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
   </bookViews>
   <sheets>
     <sheet name="Apuração" sheetId="9" r:id="rId1"/>
@@ -9515,6 +9515,45 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -9731,45 +9770,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10529,24 +10529,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="74">
   <autoFilter ref="B30:I34" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5330A6FC-1100-458A-AA09-9E9F571349FC}" name="TODOS"/>
-    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="88" dataCellStyle="Porcentagem"/>
-    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="87" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="86" dataCellStyle="Porcentagem"/>
-    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="85" dataCellStyle="Porcentagem"/>
-    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="84" dataCellStyle="Porcentagem"/>
-    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="83" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="82" dataCellStyle="Porcentagem"/>
+    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="73" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="72" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="71" dataCellStyle="Porcentagem"/>
+    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="70" dataCellStyle="Porcentagem"/>
+    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="69" dataCellStyle="Porcentagem"/>
+    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="68" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="67" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="66">
   <autoFilter ref="B48:D52" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{967F361C-5A9B-44CE-BA60-DBCCC368C089}" name="Estado"/>
@@ -10558,7 +10558,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
   <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}">
     <filterColumn colId="3">
       <filters>
@@ -10567,19 +10567,19 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="78"/>
-    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="75"/>
-    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="73" dataCellStyle="Vírgula"/>
-    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="72" dataCellStyle="Vírgula"/>
-    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="71" dataCellStyle="Vírgula"/>
-    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="70" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="69" dataCellStyle="Vírgula"/>
-    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="68" dataCellStyle="Porcentagem"/>
-    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="66" dataCellStyle="Porcentagem"/>
+    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="87"/>
+    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="84"/>
+    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="82" dataCellStyle="Vírgula"/>
+    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="81" dataCellStyle="Vírgula"/>
+    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="80" dataCellStyle="Vírgula"/>
+    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="79" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="78" dataCellStyle="Vírgula"/>
+    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="77" dataCellStyle="Porcentagem"/>
+    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="76"/>
+    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="75" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
+++ b/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b234acbc490037a6/Desktop/Projetos/Uni.co/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F59B22-2DA0-40D5-A35D-413E3E39D3EA}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1CF2696-3436-4A9C-948C-1872A7933138}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="585" windowWidth="14355" windowHeight="9075" activeTab="1" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
   </bookViews>
   <sheets>
     <sheet name="Apuração" sheetId="9" r:id="rId1"/>
@@ -8993,157 +8993,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0042E7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -9515,45 +9364,6 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -9770,6 +9580,196 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0042E7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="hair">
+          <color auto="1"/>
+        </left>
+        <right style="hair">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10529,24 +10529,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="80">
   <autoFilter ref="B30:I34" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5330A6FC-1100-458A-AA09-9E9F571349FC}" name="TODOS"/>
-    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="73" dataCellStyle="Porcentagem"/>
-    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="72" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="71" dataCellStyle="Porcentagem"/>
-    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="70" dataCellStyle="Porcentagem"/>
-    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="69" dataCellStyle="Porcentagem"/>
-    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="68" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="67" dataCellStyle="Porcentagem"/>
+    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="79" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="78" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="77" dataCellStyle="Porcentagem"/>
+    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="76" dataCellStyle="Porcentagem"/>
+    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="75" dataCellStyle="Porcentagem"/>
+    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="74" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="73" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="72">
   <autoFilter ref="B48:D52" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{967F361C-5A9B-44CE-BA60-DBCCC368C089}" name="Estado"/>
@@ -10558,7 +10558,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}">
     <filterColumn colId="3">
       <filters>
@@ -10567,71 +10567,71 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="87"/>
-    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="85"/>
-    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="84"/>
-    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="82" dataCellStyle="Vírgula"/>
-    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="81" dataCellStyle="Vírgula"/>
-    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="80" dataCellStyle="Vírgula"/>
-    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="79" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="78" dataCellStyle="Vírgula"/>
-    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="77" dataCellStyle="Porcentagem"/>
-    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="76"/>
-    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="75" dataCellStyle="Porcentagem"/>
+    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="64" dataCellStyle="Vírgula"/>
+    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="63" dataCellStyle="Vírgula"/>
+    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="62" dataCellStyle="Vírgula"/>
+    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="61" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="60" dataCellStyle="Vírgula"/>
+    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="59" dataCellStyle="Porcentagem"/>
+    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="57" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="B8:K320" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="55"/>
-    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="54" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="45" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}" name="TB_SORTIMENTO_NUM" displayName="TB_SORTIMENTO_NUM" ref="B8:I85" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}" name="TB_SORTIMENTO_NUM" displayName="TB_SORTIMENTO_NUM" ref="B8:I85" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="B8:I85" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F012D9F9-4AA9-4DD8-8D2C-386F463D46BD}" name="Região do Sortimento" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{C930A51D-467F-4F88-99D7-DC0DAF4C88DC}" name="AE" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{2172EEA3-6E07-439C-9317-D4BC4CD2DB72}" name="BU" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{E392C421-19F5-455C-BB4E-F901EBE62E4D}" name="Categoria" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{0E460137-2D05-4B06-ACE2-BE9A10A7F8EB}" name="PPA" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{09F3908B-349C-408C-BD3B-111223AC241F}" name="Qtde de Lojas da Numérica A e B" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{D35D2950-2C90-4B51-8B9F-9F281297DAD7}" name="Qtde de Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{88E10F0B-E51E-4A14-9392-78DBAECBE14A}" name="% das Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="44" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{F012D9F9-4AA9-4DD8-8D2C-386F463D46BD}" name="Região do Sortimento" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{C930A51D-467F-4F88-99D7-DC0DAF4C88DC}" name="AE" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{2172EEA3-6E07-439C-9317-D4BC4CD2DB72}" name="BU" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{E392C421-19F5-455C-BB4E-F901EBE62E4D}" name="Categoria" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{0E460137-2D05-4B06-ACE2-BE9A10A7F8EB}" name="PPA" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{09F3908B-349C-408C-BD3B-111223AC241F}" name="Qtde de Lojas da Numérica A e B" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{D35D2950-2C90-4B51-8B9F-9F281297DAD7}" name="Qtde de Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{88E10F0B-E51E-4A14-9392-78DBAECBE14A}" name="% das Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="35" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}" name="TB_EANS_PPA" displayName="TB_EANS_PPA" ref="B8:H934" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}" name="TB_EANS_PPA" displayName="TB_EANS_PPA" ref="B8:H934" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
   <autoFilter ref="B8:H934" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA0D1BC5-0C18-4157-92A9-CCCBDF42516D}" name="Região do Sortimento" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{F77A144A-8119-460F-ADF0-928B6A88BB30}" name="AE" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{D1AD7BA7-0288-4906-8914-B01801D72609}" name="BU" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{5C5C0594-8D3E-4AAA-BF64-C6A5C37F990F}" name="Categoria" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{004D5BE0-7D5A-472C-9294-8455DF372558}" name="PPA" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{B0A59FAE-56CE-4E50-94C5-291E32EB73ED}" name="Descrição" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{CC413941-E897-43BE-B4DC-8432EA5C62DE}" name="EAN Regular " dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{EA0D1BC5-0C18-4157-92A9-CCCBDF42516D}" name="Região do Sortimento" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{F77A144A-8119-460F-ADF0-928B6A88BB30}" name="AE" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{D1AD7BA7-0288-4906-8914-B01801D72609}" name="BU" dataDxfId="85"/>
+    <tableColumn id="4" xr3:uid="{5C5C0594-8D3E-4AAA-BF64-C6A5C37F990F}" name="Categoria" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{004D5BE0-7D5A-472C-9294-8455DF372558}" name="PPA" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{B0A59FAE-56CE-4E50-94C5-291E32EB73ED}" name="Descrição" dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{CC413941-E897-43BE-B4DC-8432EA5C62DE}" name="EAN Regular " dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
+++ b/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b234acbc490037a6/Desktop/Projetos/Uni.co/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1CF2696-3436-4A9C-948C-1872A7933138}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7273DB6-F233-4A41-A1E0-161F3854E59A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
   </bookViews>
   <sheets>
     <sheet name="Apuração" sheetId="9" r:id="rId1"/>
@@ -8592,268 +8592,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0042E7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -8947,6 +8685,157 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0042E7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="hair">
+          <color auto="1"/>
+        </left>
+        <right style="hair">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -9628,12 +9517,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9643,11 +9531,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
     </dxf>
     <dxf>
       <font>
@@ -9657,11 +9545,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
     </dxf>
     <dxf>
       <font>
@@ -9671,11 +9559,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
     </dxf>
     <dxf>
       <font>
@@ -9685,11 +9573,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9699,11 +9587,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9713,11 +9601,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9727,12 +9615,124 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10529,24 +10529,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="72">
   <autoFilter ref="B30:I34" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5330A6FC-1100-458A-AA09-9E9F571349FC}" name="TODOS"/>
-    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="79" dataCellStyle="Porcentagem"/>
-    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="78" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="77" dataCellStyle="Porcentagem"/>
-    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="76" dataCellStyle="Porcentagem"/>
-    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="75" dataCellStyle="Porcentagem"/>
-    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="74" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="73" dataCellStyle="Porcentagem"/>
+    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="71" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="70" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="69" dataCellStyle="Porcentagem"/>
+    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="68" dataCellStyle="Porcentagem"/>
+    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="67" dataCellStyle="Porcentagem"/>
+    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="66" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="65" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="64">
   <autoFilter ref="B48:D52" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{967F361C-5A9B-44CE-BA60-DBCCC368C089}" name="Estado"/>
@@ -10558,120 +10558,117 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
-  <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="BW"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:N33">
+    <sortCondition ref="D9:D33"/>
+  </sortState>
   <tableColumns count="13">
-    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="69"/>
-    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="64" dataCellStyle="Vírgula"/>
-    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="63" dataCellStyle="Vírgula"/>
-    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="62" dataCellStyle="Vírgula"/>
-    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="61" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="60" dataCellStyle="Vírgula"/>
-    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="59" dataCellStyle="Porcentagem"/>
-    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="57" dataCellStyle="Porcentagem"/>
+    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="56" dataCellStyle="Vírgula"/>
+    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="55" dataCellStyle="Vírgula"/>
+    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="54" dataCellStyle="Vírgula"/>
+    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="53" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="52" dataCellStyle="Vírgula"/>
+    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="51" dataCellStyle="Porcentagem"/>
+    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="49" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="B8:K320" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="45" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="37" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}" name="TB_SORTIMENTO_NUM" displayName="TB_SORTIMENTO_NUM" ref="B8:I85" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}" name="TB_SORTIMENTO_NUM" displayName="TB_SORTIMENTO_NUM" ref="B8:I85" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
   <autoFilter ref="B8:I85" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F012D9F9-4AA9-4DD8-8D2C-386F463D46BD}" name="Região do Sortimento" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{C930A51D-467F-4F88-99D7-DC0DAF4C88DC}" name="AE" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{2172EEA3-6E07-439C-9317-D4BC4CD2DB72}" name="BU" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{E392C421-19F5-455C-BB4E-F901EBE62E4D}" name="Categoria" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{0E460137-2D05-4B06-ACE2-BE9A10A7F8EB}" name="PPA" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{09F3908B-349C-408C-BD3B-111223AC241F}" name="Qtde de Lojas da Numérica A e B" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{D35D2950-2C90-4B51-8B9F-9F281297DAD7}" name="Qtde de Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{88E10F0B-E51E-4A14-9392-78DBAECBE14A}" name="% das Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="35" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{F012D9F9-4AA9-4DD8-8D2C-386F463D46BD}" name="Região do Sortimento" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{C930A51D-467F-4F88-99D7-DC0DAF4C88DC}" name="AE" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{2172EEA3-6E07-439C-9317-D4BC4CD2DB72}" name="BU" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{E392C421-19F5-455C-BB4E-F901EBE62E4D}" name="Categoria" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{0E460137-2D05-4B06-ACE2-BE9A10A7F8EB}" name="PPA" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{09F3908B-349C-408C-BD3B-111223AC241F}" name="Qtde de Lojas da Numérica A e B" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{D35D2950-2C90-4B51-8B9F-9F281297DAD7}" name="Qtde de Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{88E10F0B-E51E-4A14-9392-78DBAECBE14A}" name="% das Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="27" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}" name="TB_EANS_PPA" displayName="TB_EANS_PPA" ref="B8:H934" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}" name="TB_EANS_PPA" displayName="TB_EANS_PPA" ref="B8:H934" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="B8:H934" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA0D1BC5-0C18-4157-92A9-CCCBDF42516D}" name="Região do Sortimento" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{F77A144A-8119-460F-ADF0-928B6A88BB30}" name="AE" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{D1AD7BA7-0288-4906-8914-B01801D72609}" name="BU" dataDxfId="85"/>
-    <tableColumn id="4" xr3:uid="{5C5C0594-8D3E-4AAA-BF64-C6A5C37F990F}" name="Categoria" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{004D5BE0-7D5A-472C-9294-8455DF372558}" name="PPA" dataDxfId="83"/>
-    <tableColumn id="6" xr3:uid="{B0A59FAE-56CE-4E50-94C5-291E32EB73ED}" name="Descrição" dataDxfId="82"/>
-    <tableColumn id="7" xr3:uid="{CC413941-E897-43BE-B4DC-8432EA5C62DE}" name="EAN Regular " dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{EA0D1BC5-0C18-4157-92A9-CCCBDF42516D}" name="Região do Sortimento" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{F77A144A-8119-460F-ADF0-928B6A88BB30}" name="AE" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{D1AD7BA7-0288-4906-8914-B01801D72609}" name="BU" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{5C5C0594-8D3E-4AAA-BF64-C6A5C37F990F}" name="Categoria" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{004D5BE0-7D5A-472C-9294-8455DF372558}" name="PPA" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{B0A59FAE-56CE-4E50-94C5-291E32EB73ED}" name="Descrição" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{CC413941-E897-43BE-B4DC-8432EA5C62DE}" name="EAN Regular " dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F74CCB61-2747-4EC0-BA98-BA1A690A74E3}" name="TB_METAS_EXECUCAO" displayName="TB_METAS_EXECUCAO" ref="B8:H20" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F74CCB61-2747-4EC0-BA98-BA1A690A74E3}" name="TB_METAS_EXECUCAO" displayName="TB_METAS_EXECUCAO" ref="B8:H20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="B8:H20" xr:uid="{F74CCB61-2747-4EC0-BA98-BA1A690A74E3}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{35BE2B13-BBB6-4203-AE52-94D75DC803C1}" name="Região" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{59B5CFC4-6263-410E-AEDF-32B3D2510409}" name="Sub Região" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{E1D77274-B596-4042-BB98-67D2E502A017}" name="AE" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{6D52BC77-84B2-44A6-942B-F70BA6E5862D}" name="BU" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{4090C591-09C2-469C-A7A1-7C9D4902862E}" name="Tipo" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{7BC1FC40-8F4C-46EA-859A-9C287E5C80C0}" name="Pergunta" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{A5AFCDEF-ACC9-4079-8CFB-542D728A4CB7}" name="Preço Máximo" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{35BE2B13-BBB6-4203-AE52-94D75DC803C1}" name="Região" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{59B5CFC4-6263-410E-AEDF-32B3D2510409}" name="Sub Região" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{E1D77274-B596-4042-BB98-67D2E502A017}" name="AE" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{6D52BC77-84B2-44A6-942B-F70BA6E5862D}" name="BU" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{4090C591-09C2-469C-A7A1-7C9D4902862E}" name="Tipo" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{7BC1FC40-8F4C-46EA-859A-9C287E5C80C0}" name="Pergunta" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{A5AFCDEF-ACC9-4079-8CFB-542D728A4CB7}" name="Preço Máximo" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{01AD441B-E9B3-470E-8599-0E3FBD0ED815}" name="TB_RESUMO_PONDERADA" displayName="TB_RESUMO_PONDERADA" ref="B8:P77" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{01AD441B-E9B3-470E-8599-0E3FBD0ED815}" name="TB_RESUMO_PONDERADA" displayName="TB_RESUMO_PONDERADA" ref="B8:P77" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
   <autoFilter ref="B8:P77" xr:uid="{01AD441B-E9B3-470E-8599-0E3FBD0ED815}"/>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{A46D4F84-F858-459C-8314-605CAA8F07DD}" name="Região" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{8BC18426-CF57-4A42-8232-FD62E963F233}" name="AE" dataDxfId="22"/>
-    <tableColumn id="1" xr3:uid="{545DF62A-0488-45EA-BCD3-1F8ABC917857}" name="Prefixo da Rede" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{023F084C-D83A-44D2-94A6-55EEBD500489}" name="Classificação Ponderada" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{DC0857AB-6B3E-424B-8FF1-54ED64F55DAF}" name="Qtde de Lojas na Rede" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{132A9D4E-38E6-4D3D-8599-0FA527D75CA4}" name="Nome da Rede" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{07396A1B-3096-44C4-9611-6551AA55669C}" name="Estado" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{7E893A7E-7D64-4E00-B4CF-7C98221CAE98}" name="BU" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{2D6414DC-5E33-47B5-8ECD-EF99B35C9B8E}" name="Valo Mínimo para considerar Positivada" dataDxfId="15" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{BB04E42A-B733-474A-B118-5B50ABE19CCF}" name="Valor Faturado" dataDxfId="14" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{06E34267-1084-45FE-8583-0CEDFB458CED}" name="Positivada" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{66436B88-9AEE-4212-98BA-4B65A1FBE1CA}" name="EANS" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{5975C761-E5A0-44F9-8C75-DF48EA02A1EC}" name="Qtde de Lojas que reponderam pesquisa no MiraPDV" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{4CAB3007-83D3-459E-806A-4121E45B989B}" name="Qtde de Lojas com Execução OK (Dois preços e um PE)" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{7449A1DF-B894-4392-959F-D6F4F0AF2CD5}" name="Compliance Execução (50% das Lojas com execução OK)" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{A46D4F84-F858-459C-8314-605CAA8F07DD}" name="Região" dataDxfId="87"/>
+    <tableColumn id="14" xr3:uid="{8BC18426-CF57-4A42-8232-FD62E963F233}" name="AE" dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{545DF62A-0488-45EA-BCD3-1F8ABC917857}" name="Prefixo da Rede" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{023F084C-D83A-44D2-94A6-55EEBD500489}" name="Classificação Ponderada" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{DC0857AB-6B3E-424B-8FF1-54ED64F55DAF}" name="Qtde de Lojas na Rede" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{132A9D4E-38E6-4D3D-8599-0FA527D75CA4}" name="Nome da Rede" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{07396A1B-3096-44C4-9611-6551AA55669C}" name="Estado" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{7E893A7E-7D64-4E00-B4CF-7C98221CAE98}" name="BU" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{2D6414DC-5E33-47B5-8ECD-EF99B35C9B8E}" name="Valo Mínimo para considerar Positivada" dataDxfId="79" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{BB04E42A-B733-474A-B118-5B50ABE19CCF}" name="Valor Faturado" dataDxfId="78" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{06E34267-1084-45FE-8583-0CEDFB458CED}" name="Positivada" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{66436B88-9AEE-4212-98BA-4B65A1FBE1CA}" name="EANS" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{5975C761-E5A0-44F9-8C75-DF48EA02A1EC}" name="Qtde de Lojas que reponderam pesquisa no MiraPDV" dataDxfId="75"/>
+    <tableColumn id="12" xr3:uid="{4CAB3007-83D3-459E-806A-4121E45B989B}" name="Qtde de Lojas com Execução OK (Dois preços e um PE)" dataDxfId="74"/>
+    <tableColumn id="13" xr3:uid="{7449A1DF-B894-4392-959F-D6F4F0AF2CD5}" name="Compliance Execução (50% das Lojas com execução OK)" dataDxfId="73"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11839,7 +11836,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="89" t="s">
         <v>80</v>
       </c>
@@ -11880,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="89" t="s">
         <v>80</v>
       </c>
@@ -11888,25 +11885,25 @@
         <v>81</v>
       </c>
       <c r="D11" s="89" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E11" s="89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="89" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G11" s="109">
-        <v>17</v>
+        <v>629</v>
       </c>
       <c r="H11" s="109">
-        <v>5.0999999999999996</v>
+        <v>550</v>
       </c>
       <c r="I11" s="109">
-        <v>4.5</v>
+        <v>472</v>
       </c>
       <c r="J11" s="90">
-        <v>5.0000000000000044E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="K11" s="109">
         <v>0</v>
@@ -11921,7 +11918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="89" t="s">
         <v>80</v>
       </c>
@@ -11929,22 +11926,22 @@
         <v>81</v>
       </c>
       <c r="D12" s="89" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E12" s="89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="89" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G12" s="109">
-        <v>38</v>
+        <v>1061</v>
       </c>
       <c r="H12" s="109">
-        <v>27.4</v>
+        <v>928</v>
       </c>
       <c r="I12" s="109">
-        <v>16.899999999999999</v>
+        <v>796</v>
       </c>
       <c r="J12" s="90">
         <v>7.4999999999999997E-3</v>
@@ -11962,7 +11959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="89" t="s">
         <v>80</v>
       </c>
@@ -11970,25 +11967,25 @@
         <v>81</v>
       </c>
       <c r="D13" s="89" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E13" s="89" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F13" s="89" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G13" s="109">
-        <v>5892997</v>
+        <v>1061</v>
       </c>
       <c r="H13" s="109">
-        <v>5745672</v>
+        <v>928</v>
       </c>
       <c r="I13" s="109">
-        <v>5598347</v>
+        <v>796</v>
       </c>
       <c r="J13" s="90">
-        <v>1.4999999999999999E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="K13" s="109">
         <v>0</v>
@@ -12003,7 +12000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="89" t="s">
         <v>80</v>
       </c>
@@ -12044,7 +12041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="89" t="s">
         <v>80</v>
       </c>
@@ -12052,10 +12049,10 @@
         <v>81</v>
       </c>
       <c r="D15" s="89" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="89" t="s">
         <v>92</v>
@@ -12070,7 +12067,7 @@
         <v>12</v>
       </c>
       <c r="J15" s="90">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="K15" s="109">
         <v>0</v>
@@ -12085,7 +12082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="89" t="s">
         <v>80</v>
       </c>
@@ -12093,25 +12090,25 @@
         <v>81</v>
       </c>
       <c r="D16" s="89" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E16" s="89" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="89" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G16" s="109">
-        <v>629</v>
+        <v>17</v>
       </c>
       <c r="H16" s="109">
-        <v>550</v>
+        <v>16</v>
       </c>
       <c r="I16" s="109">
-        <v>472</v>
+        <v>15</v>
       </c>
       <c r="J16" s="90">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="K16" s="109">
         <v>0</v>
@@ -12126,7 +12123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="89" t="s">
         <v>80</v>
       </c>
@@ -12134,25 +12131,25 @@
         <v>81</v>
       </c>
       <c r="D17" s="89" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E17" s="89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="89" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G17" s="109">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H17" s="109">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I17" s="109">
-        <v>2.6</v>
+        <v>15</v>
       </c>
       <c r="J17" s="90">
-        <v>2.500000000000004E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="K17" s="109">
         <v>0</v>
@@ -12167,7 +12164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="89" t="s">
         <v>80</v>
       </c>
@@ -12175,25 +12172,25 @@
         <v>81</v>
       </c>
       <c r="D18" s="89" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E18" s="89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" s="89" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G18" s="109">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H18" s="109">
-        <v>14.6</v>
+        <v>13</v>
       </c>
       <c r="I18" s="109">
-        <v>8.1999999999999993</v>
+        <v>12</v>
       </c>
       <c r="J18" s="90">
-        <v>7.4999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="K18" s="109">
         <v>0</v>
@@ -12208,7 +12205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="89" t="s">
         <v>80</v>
       </c>
@@ -12216,25 +12213,25 @@
         <v>81</v>
       </c>
       <c r="D19" s="89" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E19" s="89" t="s">
         <v>33</v>
       </c>
       <c r="F19" s="89" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G19" s="109">
-        <v>1676424</v>
+        <v>12</v>
       </c>
       <c r="H19" s="109">
-        <v>1634513</v>
+        <v>11</v>
       </c>
       <c r="I19" s="109">
-        <v>1592603</v>
+        <v>10</v>
       </c>
       <c r="J19" s="90">
-        <v>1.4999999999999999E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="K19" s="109">
         <v>0</v>
@@ -12249,7 +12246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="89" t="s">
         <v>80</v>
       </c>
@@ -12257,10 +12254,10 @@
         <v>81</v>
       </c>
       <c r="D20" s="89" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" s="89" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F20" s="89" t="s">
         <v>92</v>
@@ -12290,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="89" t="s">
         <v>80</v>
       </c>
@@ -12301,22 +12298,22 @@
         <v>93</v>
       </c>
       <c r="E21" s="89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" s="89" t="s">
         <v>92</v>
       </c>
       <c r="G21" s="109">
+        <v>14</v>
+      </c>
+      <c r="H21" s="109">
+        <v>13</v>
+      </c>
+      <c r="I21" s="109">
         <v>12</v>
       </c>
-      <c r="H21" s="109">
-        <v>11</v>
-      </c>
-      <c r="I21" s="109">
-        <v>10</v>
-      </c>
       <c r="J21" s="90">
-        <v>7.4999999999999997E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="K21" s="109">
         <v>0</v>
@@ -12331,7 +12328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="89" t="s">
         <v>80</v>
       </c>
@@ -12339,25 +12336,25 @@
         <v>81</v>
       </c>
       <c r="D22" s="89" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E22" s="89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F22" s="89" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G22" s="109">
-        <v>1061</v>
+        <v>5892997</v>
       </c>
       <c r="H22" s="109">
-        <v>928</v>
+        <v>5745672</v>
       </c>
       <c r="I22" s="109">
-        <v>796</v>
+        <v>5598347</v>
       </c>
       <c r="J22" s="90">
-        <v>7.4999999999999997E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K22" s="109">
         <v>0</v>
@@ -12372,7 +12369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="89" t="s">
         <v>80</v>
       </c>
@@ -12380,25 +12377,25 @@
         <v>81</v>
       </c>
       <c r="D23" s="89" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E23" s="89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" s="89" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G23" s="109">
-        <v>14</v>
+        <v>1676424</v>
       </c>
       <c r="H23" s="109">
-        <v>6.5</v>
+        <v>1634513</v>
       </c>
       <c r="I23" s="109">
-        <v>5.7</v>
+        <v>1592603</v>
       </c>
       <c r="J23" s="90">
-        <v>7.5000000000000032E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K23" s="109">
         <v>0</v>
@@ -12413,7 +12410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="89" t="s">
         <v>80</v>
       </c>
@@ -12421,25 +12418,25 @@
         <v>81</v>
       </c>
       <c r="D24" s="89" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E24" s="89" t="s">
         <v>35</v>
       </c>
       <c r="F24" s="89" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G24" s="109">
-        <v>72</v>
+        <v>3898522</v>
       </c>
       <c r="H24" s="109">
-        <v>53.4</v>
+        <v>3801059</v>
       </c>
       <c r="I24" s="109">
-        <v>34.9</v>
+        <v>3703596</v>
       </c>
       <c r="J24" s="90">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="K24" s="109">
         <v>0</v>
@@ -12454,7 +12451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="89" t="s">
         <v>80</v>
       </c>
@@ -12465,19 +12462,19 @@
         <v>89</v>
       </c>
       <c r="E25" s="89" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F25" s="89" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="109">
-        <v>3898522</v>
+        <v>2463297</v>
       </c>
       <c r="H25" s="109">
-        <v>3801059</v>
+        <v>2401715</v>
       </c>
       <c r="I25" s="109">
-        <v>3703596</v>
+        <v>2340132</v>
       </c>
       <c r="J25" s="90">
         <v>1.4999999999999999E-2</v>
@@ -12495,7 +12492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="89" t="s">
         <v>80</v>
       </c>
@@ -12503,25 +12500,25 @@
         <v>81</v>
       </c>
       <c r="D26" s="89" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E26" s="89" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F26" s="89" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G26" s="109">
         <v>17</v>
       </c>
       <c r="H26" s="109">
-        <v>16</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I26" s="109">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="J26" s="90">
-        <v>2.5000000000000001E-3</v>
+        <v>5.0000000000000044E-3</v>
       </c>
       <c r="K26" s="109">
         <v>0</v>
@@ -12536,7 +12533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="89" t="s">
         <v>80</v>
       </c>
@@ -12544,25 +12541,25 @@
         <v>81</v>
       </c>
       <c r="D27" s="89" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E27" s="89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F27" s="89" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G27" s="109">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H27" s="109">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I27" s="109">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="J27" s="90">
-        <v>2.5000000000000001E-3</v>
+        <v>2.500000000000004E-3</v>
       </c>
       <c r="K27" s="109">
         <v>0</v>
@@ -12585,25 +12582,25 @@
         <v>81</v>
       </c>
       <c r="D28" s="89" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" s="89" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F28" s="89" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G28" s="109">
-        <v>1061</v>
+        <v>14</v>
       </c>
       <c r="H28" s="109">
-        <v>928</v>
+        <v>6.5</v>
       </c>
       <c r="I28" s="109">
-        <v>796</v>
+        <v>5.7</v>
       </c>
       <c r="J28" s="90">
-        <v>7.4999999999999997E-3</v>
+        <v>7.5000000000000032E-3</v>
       </c>
       <c r="K28" s="109">
         <v>0</v>
@@ -12670,22 +12667,22 @@
         <v>87</v>
       </c>
       <c r="E30" s="89" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F30" s="89" t="s">
         <v>88</v>
       </c>
       <c r="G30" s="109">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="H30" s="109">
-        <v>39.299999999999997</v>
+        <v>27.4</v>
       </c>
       <c r="I30" s="109">
-        <v>23.7</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="J30" s="90">
-        <v>5.0000000000000001E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="K30" s="109">
         <v>0</v>
@@ -12708,25 +12705,25 @@
         <v>81</v>
       </c>
       <c r="D31" s="89" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E31" s="89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" s="89" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G31" s="109">
-        <v>2463297</v>
+        <v>21</v>
       </c>
       <c r="H31" s="109">
-        <v>2401715</v>
+        <v>14.6</v>
       </c>
       <c r="I31" s="109">
-        <v>2340132</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="J31" s="90">
-        <v>1.4999999999999999E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="K31" s="109">
         <v>0</v>
@@ -12749,25 +12746,25 @@
         <v>81</v>
       </c>
       <c r="D32" s="89" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E32" s="89" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F32" s="89" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G32" s="109">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="H32" s="109">
-        <v>16</v>
+        <v>53.4</v>
       </c>
       <c r="I32" s="109">
-        <v>15</v>
+        <v>34.9</v>
       </c>
       <c r="J32" s="90">
-        <v>2.5000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="K32" s="109">
         <v>0</v>
@@ -12790,25 +12787,25 @@
         <v>81</v>
       </c>
       <c r="D33" s="89" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E33" s="89" t="s">
         <v>32</v>
       </c>
       <c r="F33" s="89" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G33" s="109">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="H33" s="109">
-        <v>13</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="I33" s="109">
-        <v>12</v>
+        <v>23.7</v>
       </c>
       <c r="J33" s="90">
-        <v>2.5000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="K33" s="109">
         <v>0</v>

--- a/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
+++ b/dados/Unico_Acompanhamento_Programa_2026-20260526092151.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b234acbc490037a6/Desktop/Projetos/Uni.co/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b234acbc490037a6/Desktop/Projetos/Unilever-Painel/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{3BFB1D67-B14B-499A-9732-AB72FC21465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7273DB6-F233-4A41-A1E0-161F3854E59A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7BEDBE9F-36BD-4617-996F-6BA139BC564D}"/>
   </bookViews>
   <sheets>
     <sheet name="Apuração" sheetId="9" r:id="rId1"/>
@@ -8592,6 +8592,268 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0042E7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="hair">
+          <color auto="1"/>
+        </left>
+        <right style="hair">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -9253,6 +9515,45 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -9469,307 +9770,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0;\-0;;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0042E7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10524,29 +10524,25 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D4995A3B-399A-4C00-B9C6-DE2CF4259F41}" name="TB_APURACAO_KPIS" displayName="TB_APURACAO_KPIS" ref="B30:I34" totalsRowShown="0" headerRowDxfId="74">
   <autoFilter ref="B30:I34" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5330A6FC-1100-458A-AA09-9E9F571349FC}" name="TODOS"/>
-    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="71" dataCellStyle="Porcentagem"/>
-    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="70" dataCellStyle="Porcentagem"/>
-    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="69" dataCellStyle="Porcentagem"/>
-    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="68" dataCellStyle="Porcentagem"/>
-    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="67" dataCellStyle="Porcentagem"/>
-    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="66" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="65" dataCellStyle="Porcentagem"/>
+    <tableColumn id="2" xr3:uid="{54095AC6-3B89-4408-BCA7-E30189BEA06F}" name="FAT." dataDxfId="73" dataCellStyle="Porcentagem"/>
+    <tableColumn id="3" xr3:uid="{9F2EE61B-726D-42A5-9FA5-9D132DC1D299}" name="Cob Pond" dataDxfId="72" dataCellStyle="Porcentagem"/>
+    <tableColumn id="4" xr3:uid="{EE5BA1D5-743E-4563-97A7-CB47D572F9F4}" name="Sort Pond" dataDxfId="71" dataCellStyle="Porcentagem"/>
+    <tableColumn id="5" xr3:uid="{9665DFFC-A9B5-4A30-BF26-34CEB3708EC5}" name="Exec Pond" dataDxfId="70" dataCellStyle="Porcentagem"/>
+    <tableColumn id="6" xr3:uid="{EFCAAFF5-77D6-43E5-AD9E-F01C06AB6C84}" name="Cob Num." dataDxfId="69" dataCellStyle="Porcentagem"/>
+    <tableColumn id="7" xr3:uid="{F1DE7AEB-3110-4C0C-BCB2-25033D309919}" name="Sort Num." dataDxfId="68" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{24D06F6C-9CE4-4368-B1E4-FB4F9AD825B3}" name="TT" dataDxfId="67" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1A724E05-604A-44A5-A7E4-14CC3D185A11}" name="TB_APURACAO_VALOR_COB" displayName="TB_APURACAO_VALOR_COB" ref="B48:D52" totalsRowShown="0" headerRowDxfId="66">
   <autoFilter ref="B48:D52" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{967F361C-5A9B-44CE-BA60-DBCCC368C089}" name="Estado"/>
@@ -10558,117 +10554,117 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}" name="TB_METAS_E_REALIZADO" displayName="TB_METAS_E_REALIZADO" ref="B9:N33" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
   <autoFilter ref="B9:N33" xr:uid="{3538589A-C376-4F8D-97E5-D5D3AC2B41BE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:N33">
     <sortCondition ref="D9:D33"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="61"/>
-    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="56" dataCellStyle="Vírgula"/>
-    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="55" dataCellStyle="Vírgula"/>
-    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="54" dataCellStyle="Vírgula"/>
-    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="53" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="52" dataCellStyle="Vírgula"/>
-    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="51" dataCellStyle="Porcentagem"/>
-    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="49" dataCellStyle="Porcentagem"/>
+    <tableColumn id="13" xr3:uid="{FB4C7745-A3A3-4599-B023-D4E2026DAEE8}" name="Região" dataDxfId="87"/>
+    <tableColumn id="1" xr3:uid="{1FBC83D7-82B4-4917-9CEB-27A0ED8B0D00}" name="AE" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{5E244AEB-29ED-471C-A8C0-C49B61F061A6}" name="KPI" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{3B82D024-860C-4283-94BC-782185EE9038}" name="BU" dataDxfId="84"/>
+    <tableColumn id="11" xr3:uid="{2C237177-FB9A-49BD-935F-D25E388F1AAD}" name="Unidade de Medida" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{86263374-3091-4ADB-B592-40FBF93E4BCC}" name="(100% do ganho)" dataDxfId="82" dataCellStyle="Vírgula"/>
+    <tableColumn id="5" xr3:uid="{AC6DF6C1-4E77-40B4-B1E1-D199723EAE20}" name="(50% do ganho)" dataDxfId="81" dataCellStyle="Vírgula"/>
+    <tableColumn id="6" xr3:uid="{115B3377-8C6A-4CAD-911C-CE0C28CD86C2}" name=" (30% do ganho)" dataDxfId="80" dataCellStyle="Vírgula"/>
+    <tableColumn id="7" xr3:uid="{48DB6C35-BA8D-45F8-B75D-187899B8AAB7}" name="Potencial Ganho" dataDxfId="79" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{204A3A88-CA1E-411E-87F3-6AD68B4C665A}" name="Realizado" dataDxfId="78" dataCellStyle="Vírgula"/>
+    <tableColumn id="12" xr3:uid="{F8B1F140-7557-42E9-9EB2-F9C84D44463C}" name="% da Meta 1" dataDxfId="77" dataCellStyle="Porcentagem"/>
+    <tableColumn id="9" xr3:uid="{C5C90530-3009-4EE8-A0BB-6CC540C29A70}" name="Faixa" dataDxfId="76"/>
+    <tableColumn id="10" xr3:uid="{ABB3BEA4-8878-4B21-A57A-117D2F42B3B4}" name="Ganho" dataDxfId="75" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}" name="TB_SORTIMENTO_POND" displayName="TB_SORTIMENTO_POND" ref="B8:K320" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="B8:K320" xr:uid="{6AF76526-113C-4232-9C7F-ED21D262E981}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="37" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{70462B59-80DF-47F8-85D2-4C0EED5CBA92}" name="Região do Sortimento" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{0581EADB-E1D8-4D4E-AB1F-ABCF66C6251A}" name="AE" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{AB652728-0371-4E9E-BD35-635796DB6706}" name="BU" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{B812C714-D502-4F4C-81F2-1ED7917A6DB4}" name="Categoria" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{BFCBCFB7-E329-4C9C-BB74-C29505AFEFD3}" name="Descricao" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{9A678B47-CE8D-4B34-8C0B-AA45CC0D7372}" name="EAN Regular" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{20C660B7-A423-4EA8-9D57-51C188EA5796}" name="Outros EANS válidos" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{610B1D60-4A29-4D4A-B187-CD0DD9DFD8AB}" name="Total de Redes" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{DBBC44BA-00D7-41A2-94B7-7F8EE7295D19}" name="Redes com Compra no mês" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{0DAF926D-EBFC-47D3-BFA6-0965BE18D7B1}" name="% das Redes" dataDxfId="54" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}" name="TB_SORTIMENTO_NUM" displayName="TB_SORTIMENTO_NUM" ref="B8:I85" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}" name="TB_SORTIMENTO_NUM" displayName="TB_SORTIMENTO_NUM" ref="B8:I85" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="B8:I85" xr:uid="{89653739-F875-4D30-A6D4-143F605A695B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F012D9F9-4AA9-4DD8-8D2C-386F463D46BD}" name="Região do Sortimento" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{C930A51D-467F-4F88-99D7-DC0DAF4C88DC}" name="AE" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{2172EEA3-6E07-439C-9317-D4BC4CD2DB72}" name="BU" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{E392C421-19F5-455C-BB4E-F901EBE62E4D}" name="Categoria" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{0E460137-2D05-4B06-ACE2-BE9A10A7F8EB}" name="PPA" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{09F3908B-349C-408C-BD3B-111223AC241F}" name="Qtde de Lojas da Numérica A e B" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{D35D2950-2C90-4B51-8B9F-9F281297DAD7}" name="Qtde de Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{88E10F0B-E51E-4A14-9392-78DBAECBE14A}" name="% das Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="27" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{F012D9F9-4AA9-4DD8-8D2C-386F463D46BD}" name="Região do Sortimento" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{C930A51D-467F-4F88-99D7-DC0DAF4C88DC}" name="AE" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{2172EEA3-6E07-439C-9317-D4BC4CD2DB72}" name="BU" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{E392C421-19F5-455C-BB4E-F901EBE62E4D}" name="Categoria" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{0E460137-2D05-4B06-ACE2-BE9A10A7F8EB}" name="PPA" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{09F3908B-349C-408C-BD3B-111223AC241F}" name="Qtde de Lojas da Numérica A e B" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{D35D2950-2C90-4B51-8B9F-9F281297DAD7}" name="Qtde de Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{88E10F0B-E51E-4A14-9392-78DBAECBE14A}" name="% das Lojas da Numérica A e B com compra do PPA no bimestre móvel" dataDxfId="44" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}" name="TB_EANS_PPA" displayName="TB_EANS_PPA" ref="B8:H934" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}" name="TB_EANS_PPA" displayName="TB_EANS_PPA" ref="B8:H934" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="B8:H934" xr:uid="{12A47C04-14E2-46CF-A2C3-37D7752CFC50}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA0D1BC5-0C18-4157-92A9-CCCBDF42516D}" name="Região do Sortimento" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{F77A144A-8119-460F-ADF0-928B6A88BB30}" name="AE" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{D1AD7BA7-0288-4906-8914-B01801D72609}" name="BU" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{5C5C0594-8D3E-4AAA-BF64-C6A5C37F990F}" name="Categoria" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{004D5BE0-7D5A-472C-9294-8455DF372558}" name="PPA" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{B0A59FAE-56CE-4E50-94C5-291E32EB73ED}" name="Descrição" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{CC413941-E897-43BE-B4DC-8432EA5C62DE}" name="EAN Regular " dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{EA0D1BC5-0C18-4157-92A9-CCCBDF42516D}" name="Região do Sortimento" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{F77A144A-8119-460F-ADF0-928B6A88BB30}" name="AE" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{D1AD7BA7-0288-4906-8914-B01801D72609}" name="BU" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{5C5C0594-8D3E-4AAA-BF64-C6A5C37F990F}" name="Categoria" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{004D5BE0-7D5A-472C-9294-8455DF372558}" name="PPA" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{B0A59FAE-56CE-4E50-94C5-291E32EB73ED}" name="Descrição" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{CC413941-E897-43BE-B4DC-8432EA5C62DE}" name="EAN Regular " dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F74CCB61-2747-4EC0-BA98-BA1A690A74E3}" name="TB_METAS_EXECUCAO" displayName="TB_METAS_EXECUCAO" ref="B8:H20" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F74CCB61-2747-4EC0-BA98-BA1A690A74E3}" name="TB_METAS_EXECUCAO" displayName="TB_METAS_EXECUCAO" ref="B8:H20" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="B8:H20" xr:uid="{F74CCB61-2747-4EC0-BA98-BA1A690A74E3}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{35BE2B13-BBB6-4203-AE52-94D75DC803C1}" name="Região" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{59B5CFC4-6263-410E-AEDF-32B3D2510409}" name="Sub Região" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{E1D77274-B596-4042-BB98-67D2E502A017}" name="AE" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{6D52BC77-84B2-44A6-942B-F70BA6E5862D}" name="BU" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{4090C591-09C2-469C-A7A1-7C9D4902862E}" name="Tipo" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{7BC1FC40-8F4C-46EA-859A-9C287E5C80C0}" name="Pergunta" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{A5AFCDEF-ACC9-4079-8CFB-542D728A4CB7}" name="Preço Máximo" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{35BE2B13-BBB6-4203-AE52-94D75DC803C1}" name="Região" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{59B5CFC4-6263-410E-AEDF-32B3D2510409}" name="Sub Região" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{E1D77274-B596-4042-BB98-67D2E502A017}" name="AE" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{6D52BC77-84B2-44A6-942B-F70BA6E5862D}" name="BU" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{4090C591-09C2-469C-A7A1-7C9D4902862E}" name="Tipo" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{7BC1FC40-8F4C-46EA-859A-9C287E5C80C0}" name="Pergunta" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{A5AFCDEF-ACC9-4079-8CFB-542D728A4CB7}" name="Preço Máximo" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{01AD441B-E9B3-470E-8599-0E3FBD0ED815}" name="TB_RESUMO_PONDERADA" displayName="TB_RESUMO_PONDERADA" ref="B8:P77" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{01AD441B-E9B3-470E-8599-0E3FBD0ED815}" name="TB_RESUMO_PONDERADA" displayName="TB_RESUMO_PONDERADA" ref="B8:P77" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="B8:P77" xr:uid="{01AD441B-E9B3-470E-8599-0E3FBD0ED815}"/>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{A46D4F84-F858-459C-8314-605CAA8F07DD}" name="Região" dataDxfId="87"/>
-    <tableColumn id="14" xr3:uid="{8BC18426-CF57-4A42-8232-FD62E963F233}" name="AE" dataDxfId="86"/>
-    <tableColumn id="1" xr3:uid="{545DF62A-0488-45EA-BCD3-1F8ABC917857}" name="Prefixo da Rede" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{023F084C-D83A-44D2-94A6-55EEBD500489}" name="Classificação Ponderada" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{DC0857AB-6B3E-424B-8FF1-54ED64F55DAF}" name="Qtde de Lojas na Rede" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{132A9D4E-38E6-4D3D-8599-0FA527D75CA4}" name="Nome da Rede" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{07396A1B-3096-44C4-9611-6551AA55669C}" name="Estado" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{7E893A7E-7D64-4E00-B4CF-7C98221CAE98}" name="BU" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{2D6414DC-5E33-47B5-8ECD-EF99B35C9B8E}" name="Valo Mínimo para considerar Positivada" dataDxfId="79" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{BB04E42A-B733-474A-B118-5B50ABE19CCF}" name="Valor Faturado" dataDxfId="78" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{06E34267-1084-45FE-8583-0CEDFB458CED}" name="Positivada" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{66436B88-9AEE-4212-98BA-4B65A1FBE1CA}" name="EANS" dataDxfId="76"/>
-    <tableColumn id="11" xr3:uid="{5975C761-E5A0-44F9-8C75-DF48EA02A1EC}" name="Qtde de Lojas que reponderam pesquisa no MiraPDV" dataDxfId="75"/>
-    <tableColumn id="12" xr3:uid="{4CAB3007-83D3-459E-806A-4121E45B989B}" name="Qtde de Lojas com Execução OK (Dois preços e um PE)" dataDxfId="74"/>
-    <tableColumn id="13" xr3:uid="{7449A1DF-B894-4392-959F-D6F4F0AF2CD5}" name="Compliance Execução (50% das Lojas com execução OK)" dataDxfId="73"/>
+    <tableColumn id="15" xr3:uid="{A46D4F84-F858-459C-8314-605CAA8F07DD}" name="Região" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{8BC18426-CF57-4A42-8232-FD62E963F233}" name="AE" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{545DF62A-0488-45EA-BCD3-1F8ABC917857}" name="Prefixo da Rede" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{023F084C-D83A-44D2-94A6-55EEBD500489}" name="Classificação Ponderada" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{DC0857AB-6B3E-424B-8FF1-54ED64F55DAF}" name="Qtde de Lojas na Rede" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{132A9D4E-38E6-4D3D-8599-0FA527D75CA4}" name="Nome da Rede" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{07396A1B-3096-44C4-9611-6551AA55669C}" name="Estado" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{7E893A7E-7D64-4E00-B4CF-7C98221CAE98}" name="BU" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{2D6414DC-5E33-47B5-8ECD-EF99B35C9B8E}" name="Valo Mínimo para considerar Positivada" dataDxfId="15" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{BB04E42A-B733-474A-B118-5B50ABE19CCF}" name="Valor Faturado" dataDxfId="14" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{06E34267-1084-45FE-8583-0CEDFB458CED}" name="Positivada" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{66436B88-9AEE-4212-98BA-4B65A1FBE1CA}" name="EANS" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{5975C761-E5A0-44F9-8C75-DF48EA02A1EC}" name="Qtde de Lojas que reponderam pesquisa no MiraPDV" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{4CAB3007-83D3-459E-806A-4121E45B989B}" name="Qtde de Lojas com Execução OK (Dois preços e um PE)" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{7449A1DF-B894-4392-959F-D6F4F0AF2CD5}" name="Compliance Execução (50% das Lojas com execução OK)" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
